--- a/report/downloads/reports/网点变化对比报告_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（51家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（33家）" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（25条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -478,7 +478,7 @@
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,23 +719,23 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>-18</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-100.0%</t>
+      <c r="C12" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -875,14 +875,14 @@
         <v>8734</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8701</v>
+        <v>8719</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-33</v>
+        <v>-15</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
@@ -6332,297 +6332,297 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="inlineStr">
+      <c r="A259" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B259" s="2" t="inlineStr">
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E259" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E260" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E261" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E262" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D265" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E265" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D266" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E266" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
         <is>
           <t>浙江</t>
         </is>
       </c>
-      <c r="C259" s="2" t="n">
+      <c r="C267" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D259" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E259" s="2" t="n">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
+      <c r="D267" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E267" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D260" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E260" s="2" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E268" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B261" s="2" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C261" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D261" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E261" s="2" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D269" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E269" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B262" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C262" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D262" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E262" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E270" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B263" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C263" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D263" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E263" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D271" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E271" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C264" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D264" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E264" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B265" s="2" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C265" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D265" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E265" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B266" s="2" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C266" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D266" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E266" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B267" s="2" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C267" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D267" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E267" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D268" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E268" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B269" s="2" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C269" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D269" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E269" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B270" s="2" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C270" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D270" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E270" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B271" s="2" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="C271" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D271" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E271" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B272" s="2" t="inlineStr">
+      <c r="B272" s="3" t="inlineStr">
         <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C272" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D272" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E272" s="2" t="n">
-        <v>-1</v>
+      <c r="C272" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
     </row>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
     </row>
@@ -11314,174 +11314,174 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>意特汽车商业（上海）有限公司</t>
+          <t>深圳罗湖KKMALL体验店</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>恒通东路69号101单元 龙盛福新汇 上海 上海</t>
+          <t>广东省深圳市罗湖区桂园街道深南东路5016号KKMALL一层L112/112A3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>昆明乐骏汽车销售服务有限公司</t>
+          <t>贵阳方圆荟海豚广场</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>昆明市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>滇池度假区滇池路1103号平安大厦B座1层 平安大厦 昆明市 滇池度假区</t>
+          <t>贵州省贵阳市南明区花果园大街88号1F-SN007铺位</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>北京骏东汽车销售服务有限公司</t>
+          <t>西安曲江大悦城体验店</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>西安市</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>金宝街 金宝大厦一层 北京 东城区</t>
+          <t>陕西省西安市雁塔区慈恩西路777号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>成都骏意汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>成都市</t>
+          <t>威海市</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>成都市高新区火车南站西路 法拉利 成都市 中国</t>
+          <t>山东省威海市环翠区经技技术开发区青岛南路242号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>安徽鸿粤鸿超汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>合肥市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>花亭湖路与齐云山路交叉口 安徽鸿粤鸿超汽车销售服务有限公司 合肥 蜀山区</t>
+          <t>山西省晋中市山西综改示范区晋中开发区汇通产业园区汇通北路1060号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>青岛恒骏汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•东莞虎门鸿熙汽车城</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>东莞市</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>青岛市市南区东海西路1号1号楼丙户 青岛市 市南区</t>
+          <t>广东省东莞市虎门镇博涌社区社岗村S358省道旁</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>广东骏佳汽车服务有限公司</t>
+          <t>华为授权体验店（新塘永旺）</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -11495,492 +11495,6 @@
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>天河区珠江新城清风街1-48号 新世界广场首层 Guangzhou</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>骏佳行汽车服务（深圳）有限公司</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>深圳市</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>中心路1号 深圳湾壹号北区2栋 Shenzhen Nanshan District</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>南京瑞骏汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>南京市</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>长江路100号 长江会 南京 玄武</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>苏州意骏汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>苏州市</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>苏州工业园区思安街99号协鑫广场西侧1F Suzhou</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>宁波骏意汽车服务有限公司</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>宁波市</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>中官新路 A号楼 Ningbo Jiangbei District</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>杭州骏意汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>杭州市</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>浙江省杭州市南山路 杭州 上城区</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>温州骏意汽车服务有限公司</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>温州市</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>温州经济技术开发区滨海园区 3号4S店东侧 温州 中国</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>武汉骏东汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>武汉市</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>解放大道634号K11步行街 108-109 武汉 中国</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>长沙市骏马汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>长沙市</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>潇湘北路 圆泰长沙印 103-1 号 长沙市 中国</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>福建骏佳行汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>厦门市</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>环岛东路1821号 中航紫金广场商业街 厦门市 思明区</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>重庆骏东汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>重庆两江新区新南路 龙湖晶郦馆A栋-1F-03b Chongqing New South St</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>西安市</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>深圳罗湖KKMALL体验店</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>深圳市</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>广东省深圳市罗湖区桂园街道深南东路5016号KKMALL一层L112/112A3</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>贵阳方圆荟海豚广场</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>贵阳市</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>贵州省贵阳市南明区花果园大街88号1F-SN007铺位</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>西安曲江大悦城体验店</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>西安市</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>陕西省西安市雁塔区慈恩西路777号</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>威海市</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>山东省威海市环翠区经技技术开发区青岛南路242号</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>晋中市</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>山西省晋中市山西综改示范区晋中开发区汇通产业园区汇通北路1060号</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•东莞虎门鸿熙汽车城</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>东莞市</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>广东省东莞市虎门镇博涌社区社岗村S358省道旁</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>华为授权体验店（新塘永旺）</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>广东省广州市增城区新塘永旺1楼华为授权体验店（西町村屋对面）</t>
         </is>
@@ -12043,22 +11557,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12068,29 +11582,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12100,29 +11614,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12132,7 +11646,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -12171,22 +11685,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12196,7 +11710,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
@@ -12235,22 +11749,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12260,29 +11774,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12292,29 +11806,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12324,29 +11838,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12356,7 +11870,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -12368,17 +11882,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12388,29 +11902,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12420,29 +11934,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12452,29 +11966,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12484,29 +11998,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12516,7 +12030,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
@@ -12555,22 +12069,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12587,22 +12101,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12619,22 +12133,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12651,7 +12165,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -12661,12 +12175,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12693,12 +12207,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12715,7 +12229,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -12725,12 +12239,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12747,22 +12261,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12779,22 +12293,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615.xlsx
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
     </row>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
     </row>
@@ -11557,22 +11557,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
@@ -11594,17 +11594,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11614,29 +11614,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11658,17 +11658,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11678,29 +11678,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11710,29 +11710,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11742,29 +11742,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -11786,17 +11786,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11806,29 +11806,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11838,29 +11838,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11870,29 +11870,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -11914,17 +11914,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
@@ -11973,22 +11973,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11998,29 +11998,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -12069,22 +12069,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12101,22 +12101,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12133,22 +12133,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12165,22 +12165,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12207,12 +12207,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12234,17 +12234,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12261,22 +12261,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615.xlsx
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -11557,22 +11557,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
@@ -11594,17 +11594,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11614,14 +11614,14 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -11631,12 +11631,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11646,29 +11646,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11678,29 +11678,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11710,29 +11710,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11742,29 +11742,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11774,29 +11774,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11806,29 +11806,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11838,29 +11838,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11870,29 +11870,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11902,29 +11902,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11934,29 +11934,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11966,29 +11966,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11998,29 +11998,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
         </is>
       </c>
     </row>
@@ -12069,22 +12069,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12101,22 +12101,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12133,22 +12133,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12165,22 +12165,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12202,17 +12202,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12234,17 +12234,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12261,22 +12261,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
